--- a/xls/square_20_tri3_20.xlsx
+++ b/xls/square_20_tri3_20.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18">
+        <v>441</v>
+      </c>
+      <c r="C18" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18">
+        <v>441</v>
+      </c>
+      <c r="E18" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18">
+        <v>361</v>
+      </c>
+      <c r="G18" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18">
+        <v>1944</v>
+      </c>
+      <c r="I18">
+        <v>2.593184782708127</v>
+      </c>
+      <c r="J18">
+        <v>-0.7620984177108391</v>
+      </c>
+      <c r="K18">
+        <v>0.6732600601350307</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19">
+        <v>441</v>
+      </c>
+      <c r="C19" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19">
+        <v>441</v>
+      </c>
+      <c r="E19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19">
+        <v>400</v>
+      </c>
+      <c r="G19" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19">
+        <v>2166</v>
+      </c>
+      <c r="I19">
+        <v>1.146032137320716</v>
+      </c>
+      <c r="J19">
+        <v>-1.6483249275638248</v>
+      </c>
+      <c r="K19">
+        <v>-0.0335546723548859</v>
+      </c>
+    </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
         <v>11</v>
